--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Creating an Enterprise Application in Entra ID</t>
+          <t>Creating Enterprise Application in Entra ID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJFB5PFXSNTX6S024R53HHRN</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB5PFXSNTX6S024R53HHRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Application Groups</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJFB8K8DV4GRQ616DQRAJPS5</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB8K8DV4GRQ616DQRAJPS5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Groups</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Notification Rule</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,107 +781,107 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Rule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,152 +837,196 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Custom Operational Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source Configuration</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PII Attributes</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,63 +649,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Provisioning</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Groups</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Access Rules</t>
+          <t>Password Policies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,85 +759,85 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Rule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Custom Operational Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,34 +847,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Custom Operational Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,22 +595,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>h_01KRZRTP24GG27V8XGHD14MYMG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZRTP24GG27V8XGHD14MYMG</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Provisioning</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,85 +649,85 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>h_01KRZVW8GA1WQTSVXEBDNTBCDH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZVW8GA1WQTSVXEBDNTBCDH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Source Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>h_01KS09W6QCKXHB330XZKK1107F</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS09W6QCKXHB330XZKK1107F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Groups</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Access Rules</t>
+          <t>Rules</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Password Policies</t>
+          <t>Access Bundles</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PII Attributes</t>
+          <t>Assignments</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Attribute Based</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>h_01KS22H7J388N9JAHT2DH0HZX9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS22H7J388N9JAHT2DH0HZX9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Entra ID Group Based</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KS22Q6VFHJK0YVBXYYTDWY0R</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS22Q6VFHJK0YVBXYYTDWY0R</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Enterprise App Based</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>h_01KS22T2ZRSP3FTXTJR36EG4J9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS22T2ZRSP3FTXTJR36EG4J9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Custom Operational Settings</t>
+          <t>Modifying Assignment Rules</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Password Policies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KRZV598N96MG0QEM63C421B4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZV598N96MG0QEM63C421B4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Attribute Metadata</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Monitor Provisioning</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,76 +957,296 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Custom Operational Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Define notification channel</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Source Filter</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KS28PAPR0ZBAX7NXCG1XCNZ8</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS28PAPR0ZBAX7NXCG1XCNZ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Synchronization Setting</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KSFCZK0PAE4ZP4F3TJ8HBES2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFCZK0PAE4ZP4F3TJ8HBES2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multiple-Applications-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Entra ID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Source Application</t>
+          <t>Directory Instance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRZVW8GA1WQTSVXEBDNTBCDH</t>
+          <t>h_01KV57T9RSQ1THEJQGQPCFF927</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZVW8GA1WQTSVXEBDNTBCDH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KV57T9RSQ1THEJQGQPCFF927</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Source Configuration</t>
+          <t>Advanced User Filter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KS09W6QCKXHB330XZKK1107F</t>
+          <t>h_01KV580YW80NK11S6SDKW5T5SD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS09W6QCKXHB330XZKK1107F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KV580YW80NK11S6SDKW5T5SD</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KS22H7J388N9JAHT2DH0HZX9</t>
+          <t>h_01KVFJ4NVN006FS068AEFDKVYE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS22H7J388N9JAHT2DH0HZX9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KVFJ4NVN006FS068AEFDKVYE</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise App Based</t>
+          <t>Enterprise Application Based</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Modifying Assignment Rules</t>
+          <t>Expression Based</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KS2314NK832RV0ARBZB3WSEX</t>
+          <t>h_01KS22H7J388N9JAHT2DH0HZX9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS2314NK832RV0ARBZB3WSEX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS22H7J388N9JAHT2DH0HZX9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Password Policies</t>
+          <t>Modifying Assignment Rules</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PII Attributes</t>
+          <t>Password Policies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRZV598N96MG0QEM63C421B4</t>
+          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZV598N96MG0QEM63C421B4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Metadata</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>h_01KRZV598N96MG0QEM63C421B4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZV598N96MG0QEM63C421B4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Monitor Provisioning</t>
+          <t>Attribute Metadata</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,85 +935,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
+          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Monitor Provisioning</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KRZS8BC1DHDSQQGB9DHBNPWZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Custom Operational Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFC4ZFVTRT4G39ZPPS1EW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Define notification channel</t>
+          <t>Custom Operational Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KMFQFJGS57X20VCSQC1M6ZP3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Define notification channel</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KSFG2PMFCNWG64GDZZ82AXMT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KNS2NCYH8BG3B41F5XYD4P5M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Rollout Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KS28PAPR0ZBAX7NXCG1XCNZ8</t>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS28PAPR0ZBAX7NXCG1XCNZ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multiple-Applications-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Synchronization Setting</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
